--- a/Assets/Data/Excel/UnitData.xlsx
+++ b/Assets/Data/Excel/UnitData.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="31">
   <si>
     <r>
       <rPr>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">string</t>
   </si>
   <si>
-    <t xml:space="preserve">Top.UnitType[]</t>
+    <t xml:space="preserve">string[]</t>
   </si>
   <si>
     <t xml:space="preserve">Vector2Int</t>
@@ -105,9 +105,6 @@
   </si>
   <si>
     <t xml:space="preserve">bool</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string[]</t>
   </si>
   <si>
     <r>
@@ -466,12 +463,12 @@
       </c>
       <c r="L2" s="2"/>
       <c r="M2" s="2" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="16.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B3" s="2"/>
       <c r="C3" s="2"/>
@@ -481,112 +478,115 @@
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
       <c r="I3" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="J3" s="3"/>
       <c r="K3" s="3"/>
       <c r="L3" s="3"/>
       <c r="M3" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B4" s="2" t="n">
         <v>11111</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="2" t="s">
+      <c r="G4" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="G4" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="H4" s="3"/>
       <c r="I4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="J4" s="3"/>
-      <c r="K4" s="4" t="b">
+      <c r="K4" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L4" s="2"/>
       <c r="M4" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B5" s="3" t="n">
         <v>22222</v>
       </c>
       <c r="C5" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="2" t="s">
         <v>28</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>29</v>
       </c>
       <c r="E5" s="3"/>
       <c r="F5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G5" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="G5" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3" t="n">
         <v>2</v>
       </c>
       <c r="J5" s="3"/>
-      <c r="K5" s="4" t="b">
+      <c r="K5" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L5" s="2"/>
       <c r="M5" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="B6" s="3" t="n">
         <v>33333</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
       <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="G6" s="2" t="s">
         <v>23</v>
-      </c>
-      <c r="G6" s="2" t="s">
-        <v>24</v>
       </c>
       <c r="H6" s="3"/>
       <c r="I6" s="3" t="n">
         <v>3</v>
       </c>
       <c r="J6" s="3"/>
-      <c r="K6" s="4" t="b">
+      <c r="K6" s="4" t="n">
+        <f aca="false">FALSE()</f>
         <v>0</v>
       </c>
       <c r="L6" s="2"/>
       <c r="M6" s="2" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
